--- a/SeaAroundUsExtraction/global_output/regional_calculations/LME_057_Laptev_Sea.xlsx
+++ b/SeaAroundUsExtraction/global_output/regional_calculations/LME_057_Laptev_Sea.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R6431108d2eee4af2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rc6fb2c4109704fca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R6a3b2639a8904270"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R595048a8e93e4a08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rc6cfed3948704887"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R823c5f3b41994ffd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R64ed29faf7b4406e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rd1880f35a7c143b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R1394ab73d4b74864"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R96fb03a716a54b24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R02c27485a9f049c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rdc3a14a4f0284657"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.0"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -83,8 +81,7 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="22">
-    <x:border/>
+  <x:borders count="11">
     <x:border/>
     <x:border>
       <x:right style="thin">
@@ -175,101 +172,6 @@
       <x:top style="thin">
         <x:color rgb="FFD0D5DD"/>
       </x:top>
-    </x:border>
-    <x:border>
-      <x:right style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:right>
-      <x:bottom style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:right>
-      <x:bottom style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:left>
-      <x:bottom style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:right style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:left>
-      <x:top style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:right style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:top>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:top>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:left>
-      <x:top style="thin">
-        <x:color rgb="FFD0D5DD"/>
-      </x:top>
-    </x:border>
-    <x:border>
-      <x:bottom style="medium">
-        <x:color rgb="FF147D92"/>
-      </x:bottom>
     </x:border>
     <x:border>
       <x:bottom style="medium">
@@ -280,37 +182,32 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="69">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
@@ -326,77 +223,40 @@
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="201" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="202" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -407,30 +267,25 @@
         </x:patternFill>
       </x:fill>
     </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
   </x:dxfs>
 </x:styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <xfpb:bag type="Checkbox"/>
+  <xfpb:bag type="XFControls">
+    <xfpb:bagId k="CellControl">0</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplement">
+    <xfpb:bagId k="XFControls">1</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <xfpb:a k="MappedFeaturePropertyBags">
+      <xfpb:bagId>2</xfpb:bagId>
+    </xfpb:a>
+  </xfpb:bag>
+</xfpb:FeaturePropertyBags>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -464,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="LME057CommercialTable" displayName="LME057CommercialTable" ref="A1:O3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O3"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="LME057CommercialTable" displayName="LME057CommercialTable" ref="A1:E3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E3"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="LME057FunctionalTable" displayName="LME057FunctionalTable" ref="A1:O4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O4"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="LME057FunctionalTable" displayName="LME057FunctionalTable" ref="A1:E4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E4"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="LME057ValidationTable" displayName="LME057ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="LME057ValidationTable" displayName="LME057ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -743,401 +578,401 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="56" t="str">
+      <x:c r="A1" s="29" t="str">
         <x:v>unit_id</x:v>
       </x:c>
-      <x:c r="B1" s="56" t="str">
+      <x:c r="B1" s="29" t="str">
         <x:v>region_name</x:v>
       </x:c>
-      <x:c r="C1" s="56" t="str">
+      <x:c r="C1" s="29" t="str">
         <x:v>region_type</x:v>
       </x:c>
-      <x:c r="D1" s="56" t="str">
+      <x:c r="D1" s="29" t="str">
         <x:v>year</x:v>
       </x:c>
-      <x:c r="E1" s="56" t="str">
+      <x:c r="E1" s="29" t="str">
         <x:v>taxon</x:v>
       </x:c>
-      <x:c r="F1" s="56" t="str">
+      <x:c r="F1" s="29" t="str">
         <x:v>common_name</x:v>
       </x:c>
-      <x:c r="G1" s="56" t="str">
+      <x:c r="G1" s="29" t="str">
         <x:v>functional_group</x:v>
       </x:c>
-      <x:c r="H1" s="56" t="str">
+      <x:c r="H1" s="29" t="str">
         <x:v>commercial_group</x:v>
       </x:c>
-      <x:c r="I1" s="56" t="str">
+      <x:c r="I1" s="29" t="str">
         <x:v>catch_tonnes</x:v>
       </x:c>
-      <x:c r="J1" s="56" t="str">
+      <x:c r="J1" s="29" t="str">
         <x:v>landings_tonnes</x:v>
       </x:c>
-      <x:c r="K1" s="56" t="str">
+      <x:c r="K1" s="29" t="str">
         <x:v>discards_tonnes</x:v>
       </x:c>
-      <x:c r="L1" s="56" t="str">
+      <x:c r="L1" s="29" t="str">
         <x:v>reported_tonnes</x:v>
       </x:c>
-      <x:c r="M1" s="56" t="str">
+      <x:c r="M1" s="29" t="str">
         <x:v>unreported_tonnes</x:v>
       </x:c>
-      <x:c r="N1" s="56" t="str">
+      <x:c r="N1" s="29" t="str">
         <x:v>taxon_key</x:v>
       </x:c>
-      <x:c r="O1" s="56" t="str">
+      <x:c r="O1" s="29" t="str">
         <x:v>tl</x:v>
       </x:c>
-      <x:c r="P1" s="56" t="str">
+      <x:c r="P1" s="29" t="str">
         <x:v>match_method</x:v>
       </x:c>
-      <x:c r="Q1" s="56" t="str">
+      <x:c r="Q1" s="29" t="str">
         <x:v>tl_source</x:v>
       </x:c>
-      <x:c r="R1" s="56" t="str">
+      <x:c r="R1" s="29" t="str">
         <x:v>match_confidence</x:v>
       </x:c>
-      <x:c r="S1" s="56" t="str">
+      <x:c r="S1" s="29" t="str">
         <x:v>reference_taxon</x:v>
       </x:c>
-      <x:c r="T1" s="56" t="str">
+      <x:c r="T1" s="29" t="str">
         <x:v>sppr</x:v>
       </x:c>
-      <x:c r="U1" s="56" t="str">
+      <x:c r="U1" s="29" t="str">
         <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
-      <x:c r="A2" s="46" t="str">
-        <x:v>LME_057</x:v>
-      </x:c>
-      <x:c r="B2" s="46" t="str">
+      <x:c r="A2" s="24" t="str">
+        <x:v>LME_057</x:v>
+      </x:c>
+      <x:c r="B2" s="24" t="str">
         <x:v>Laptev Sea</x:v>
       </x:c>
-      <x:c r="C2" s="46" t="str">
+      <x:c r="C2" s="24" t="str">
         <x:v>LME</x:v>
       </x:c>
-      <x:c r="D2" s="58" t="n">
+      <x:c r="D2" s="30" t="n">
         <x:v>2019</x:v>
       </x:c>
-      <x:c r="E2" s="46" t="str">
+      <x:c r="E2" s="24" t="str">
         <x:v>Marine fishes not identified</x:v>
       </x:c>
-      <x:c r="F2" s="46" t="str">
+      <x:c r="F2" s="24" t="str">
         <x:v>Marine fishes nei</x:v>
       </x:c>
-      <x:c r="G2" s="46" t="str">
+      <x:c r="G2" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="H2" s="46" t="str">
+      <x:c r="H2" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="I2" s="60" t="n">
+      <x:c r="I2" s="31" t="n">
         <x:v>1128.8195392729</x:v>
       </x:c>
-      <x:c r="J2" s="60" t="n">
+      <x:c r="J2" s="31" t="n">
         <x:v>1128.8195392729</x:v>
       </x:c>
-      <x:c r="K2" s="60" t="n">
+      <x:c r="K2" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L2" s="60" t="n">
+      <x:c r="L2" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M2" s="60" t="n">
+      <x:c r="M2" s="31" t="n">
         <x:v>1128.8195392729</x:v>
       </x:c>
-      <x:c r="N2" s="46" t="str">
+      <x:c r="N2" s="24" t="str">
         <x:v>marine fishes not identified</x:v>
       </x:c>
-      <x:c r="O2" s="62" t="n">
+      <x:c r="O2" s="32" t="n">
         <x:v>3.28</x:v>
       </x:c>
-      <x:c r="P2" s="46" t="str">
+      <x:c r="P2" s="24" t="str">
         <x:v>exact_sea_around_us</x:v>
       </x:c>
-      <x:c r="Q2" s="62" t="str">
+      <x:c r="Q2" s="32" t="str">
         <x:v>Sea Around Us exploited organisms</x:v>
       </x:c>
-      <x:c r="R2" s="46" t="str">
+      <x:c r="R2" s="24" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="S2" s="46" t="str">
+      <x:c r="S2" s="24" t="str">
         <x:v>Marine fishes not identified</x:v>
       </x:c>
-      <x:c r="T2" s="62" t="n">
+      <x:c r="T2" s="32" t="n">
         <x:f>IF(O2="","",(1/'Metadata'!$B$5)^(O2-1))</x:f>
         <x:v>190.54607179632464</x:v>
       </x:c>
-      <x:c r="U2" s="60" t="n">
+      <x:c r="U2" s="31" t="n">
         <x:f>IF(T2="","",I2*T2)</x:f>
         <x:v>215092.12897538813</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
-      <x:c r="A3" s="46" t="str">
-        <x:v>LME_057</x:v>
-      </x:c>
-      <x:c r="B3" s="46" t="str">
+      <x:c r="A3" s="24" t="str">
+        <x:v>LME_057</x:v>
+      </x:c>
+      <x:c r="B3" s="24" t="str">
         <x:v>Laptev Sea</x:v>
       </x:c>
-      <x:c r="C3" s="46" t="str">
+      <x:c r="C3" s="24" t="str">
         <x:v>LME</x:v>
       </x:c>
-      <x:c r="D3" s="58" t="n">
+      <x:c r="D3" s="30" t="n">
         <x:v>2019</x:v>
       </x:c>
-      <x:c r="E3" s="46" t="str">
+      <x:c r="E3" s="24" t="str">
         <x:v>Coregonus sardinella</x:v>
       </x:c>
-      <x:c r="F3" s="46" t="str">
+      <x:c r="F3" s="24" t="str">
         <x:v>Sardine cisco</x:v>
       </x:c>
-      <x:c r="G3" s="46" t="str">
+      <x:c r="G3" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="H3" s="46" t="str">
+      <x:c r="H3" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="I3" s="60" t="n">
+      <x:c r="I3" s="31" t="n">
         <x:v>707.1833091418</x:v>
       </x:c>
-      <x:c r="J3" s="60" t="n">
+      <x:c r="J3" s="31" t="n">
         <x:v>707.1833091418</x:v>
       </x:c>
-      <x:c r="K3" s="60" t="n">
+      <x:c r="K3" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L3" s="60" t="n">
+      <x:c r="L3" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M3" s="60" t="n">
+      <x:c r="M3" s="31" t="n">
         <x:v>707.1833091418</x:v>
       </x:c>
-      <x:c r="N3" s="46" t="str">
+      <x:c r="N3" s="24" t="str">
         <x:v>coregonus sardinella</x:v>
       </x:c>
-      <x:c r="O3" s="62" t="n">
+      <x:c r="O3" s="32" t="n">
         <x:v>3.21</x:v>
       </x:c>
-      <x:c r="P3" s="46" t="str">
+      <x:c r="P3" s="24" t="str">
         <x:v>exact_2020_supplement</x:v>
       </x:c>
-      <x:c r="Q3" s="62" t="str">
+      <x:c r="Q3" s="32" t="str">
         <x:v>2020 supplement MeanTL</x:v>
       </x:c>
-      <x:c r="R3" s="46" t="str">
+      <x:c r="R3" s="24" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="S3" s="46" t="str">
+      <x:c r="S3" s="24" t="str">
         <x:v>Coregonus sardinella</x:v>
       </x:c>
-      <x:c r="T3" s="62" t="n">
+      <x:c r="T3" s="32" t="n">
         <x:f>IF(O3="","",(1/'Metadata'!$B$5)^(O3-1))</x:f>
         <x:v>162.18100973589299</x:v>
       </x:c>
-      <x:c r="U3" s="60" t="n">
+      <x:c r="U3" s="31" t="n">
         <x:f>IF(T3="","",I3*T3)</x:f>
         <x:v>114691.70314498729</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
-      <x:c r="A4" s="46" t="str">
-        <x:v>LME_057</x:v>
-      </x:c>
-      <x:c r="B4" s="46" t="str">
+      <x:c r="A4" s="24" t="str">
+        <x:v>LME_057</x:v>
+      </x:c>
+      <x:c r="B4" s="24" t="str">
         <x:v>Laptev Sea</x:v>
       </x:c>
-      <x:c r="C4" s="46" t="str">
+      <x:c r="C4" s="24" t="str">
         <x:v>LME</x:v>
       </x:c>
-      <x:c r="D4" s="58" t="n">
+      <x:c r="D4" s="30" t="n">
         <x:v>2019</x:v>
       </x:c>
-      <x:c r="E4" s="46" t="str">
+      <x:c r="E4" s="24" t="str">
         <x:v>Coregonus muksun</x:v>
       </x:c>
-      <x:c r="F4" s="46" t="str">
+      <x:c r="F4" s="24" t="str">
         <x:v>Muksun</x:v>
       </x:c>
-      <x:c r="G4" s="46" t="str">
+      <x:c r="G4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="H4" s="46" t="str">
+      <x:c r="H4" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="I4" s="60" t="n">
+      <x:c r="I4" s="31" t="n">
         <x:v>508.346393164</x:v>
       </x:c>
-      <x:c r="J4" s="60" t="n">
+      <x:c r="J4" s="31" t="n">
         <x:v>508.346393164</x:v>
       </x:c>
-      <x:c r="K4" s="60" t="n">
+      <x:c r="K4" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L4" s="60" t="n">
+      <x:c r="L4" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M4" s="60" t="n">
+      <x:c r="M4" s="31" t="n">
         <x:v>508.346393164</x:v>
       </x:c>
-      <x:c r="N4" s="46" t="str">
+      <x:c r="N4" s="24" t="str">
         <x:v>coregonus muksun</x:v>
       </x:c>
-      <x:c r="O4" s="62" t="n">
+      <x:c r="O4" s="32" t="n">
         <x:v>3.27</x:v>
       </x:c>
-      <x:c r="P4" s="46" t="str">
+      <x:c r="P4" s="24" t="str">
         <x:v>exact_sea_around_us</x:v>
       </x:c>
-      <x:c r="Q4" s="62" t="str">
+      <x:c r="Q4" s="32" t="str">
         <x:v>Sea Around Us exploited organisms</x:v>
       </x:c>
-      <x:c r="R4" s="46" t="str">
+      <x:c r="R4" s="24" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="S4" s="46" t="str">
+      <x:c r="S4" s="24" t="str">
         <x:v>Coregonus muksun</x:v>
       </x:c>
-      <x:c r="T4" s="62" t="n">
+      <x:c r="T4" s="32" t="n">
         <x:f>IF(O4="","",(1/'Metadata'!$B$5)^(O4-1))</x:f>
         <x:v>186.20871366628674</x:v>
       </x:c>
-      <x:c r="U4" s="60" t="n">
+      <x:c r="U4" s="31" t="n">
         <x:f>IF(T4="","",I4*T4)</x:f>
         <x:v>94658.5279679649</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
-      <x:c r="A5" s="46" t="str">
-        <x:v>LME_057</x:v>
-      </x:c>
-      <x:c r="B5" s="46" t="str">
+      <x:c r="A5" s="24" t="str">
+        <x:v>LME_057</x:v>
+      </x:c>
+      <x:c r="B5" s="24" t="str">
         <x:v>Laptev Sea</x:v>
       </x:c>
-      <x:c r="C5" s="46" t="str">
+      <x:c r="C5" s="24" t="str">
         <x:v>LME</x:v>
       </x:c>
-      <x:c r="D5" s="58" t="n">
+      <x:c r="D5" s="30" t="n">
         <x:v>2019</x:v>
       </x:c>
-      <x:c r="E5" s="46" t="str">
+      <x:c r="E5" s="24" t="str">
         <x:v>Coregonus</x:v>
       </x:c>
-      <x:c r="F5" s="46" t="str">
+      <x:c r="F5" s="24" t="str">
         <x:v>Whitefishes</x:v>
       </x:c>
-      <x:c r="G5" s="46" t="str">
+      <x:c r="G5" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="H5" s="46" t="str">
+      <x:c r="H5" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="I5" s="60" t="n">
+      <x:c r="I5" s="31" t="n">
         <x:v>165.8549513662</x:v>
       </x:c>
-      <x:c r="J5" s="60" t="n">
+      <x:c r="J5" s="31" t="n">
         <x:v>165.8549513662</x:v>
       </x:c>
-      <x:c r="K5" s="60" t="n">
+      <x:c r="K5" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L5" s="60" t="n">
+      <x:c r="L5" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M5" s="60" t="n">
+      <x:c r="M5" s="31" t="n">
         <x:v>165.8549513662</x:v>
       </x:c>
-      <x:c r="N5" s="46" t="str">
+      <x:c r="N5" s="24" t="str">
         <x:v>coregonus</x:v>
       </x:c>
-      <x:c r="O5" s="62" t="n">
+      <x:c r="O5" s="32" t="n">
         <x:v>3.3</x:v>
       </x:c>
-      <x:c r="P5" s="46" t="str">
+      <x:c r="P5" s="24" t="str">
         <x:v>exact_sea_around_us</x:v>
       </x:c>
-      <x:c r="Q5" s="62" t="str">
+      <x:c r="Q5" s="32" t="str">
         <x:v>Sea Around Us exploited organisms</x:v>
       </x:c>
-      <x:c r="R5" s="46" t="str">
+      <x:c r="R5" s="24" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="S5" s="46" t="str">
+      <x:c r="S5" s="24" t="str">
         <x:v>Coregonus</x:v>
       </x:c>
-      <x:c r="T5" s="62" t="n">
+      <x:c r="T5" s="32" t="n">
         <x:f>IF(O5="","",(1/'Metadata'!$B$5)^(O5-1))</x:f>
         <x:v>199.52623149688787</x:v>
       </x:c>
-      <x:c r="U5" s="60" t="n">
+      <x:c r="U5" s="31" t="n">
         <x:f>IF(T5="","",I5*T5)</x:f>
         <x:v>33092.4134211975</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
-      <x:c r="A6" s="46" t="str">
-        <x:v>LME_057</x:v>
-      </x:c>
-      <x:c r="B6" s="46" t="str">
+      <x:c r="A6" s="24" t="str">
+        <x:v>LME_057</x:v>
+      </x:c>
+      <x:c r="B6" s="24" t="str">
         <x:v>Laptev Sea</x:v>
       </x:c>
-      <x:c r="C6" s="46" t="str">
+      <x:c r="C6" s="24" t="str">
         <x:v>LME</x:v>
       </x:c>
-      <x:c r="D6" s="58" t="n">
+      <x:c r="D6" s="30" t="n">
         <x:v>2019</x:v>
       </x:c>
-      <x:c r="E6" s="46" t="str">
+      <x:c r="E6" s="24" t="str">
         <x:v>Coregonus autumnalis</x:v>
       </x:c>
-      <x:c r="F6" s="46" t="str">
+      <x:c r="F6" s="24" t="str">
         <x:v>Arctic cisco</x:v>
       </x:c>
-      <x:c r="G6" s="46" t="str">
+      <x:c r="G6" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="H6" s="46" t="str">
+      <x:c r="H6" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="I6" s="60" t="n">
+      <x:c r="I6" s="31" t="n">
         <x:v>105.9792232908</x:v>
       </x:c>
-      <x:c r="J6" s="60" t="n">
+      <x:c r="J6" s="31" t="n">
         <x:v>105.9792232908</x:v>
       </x:c>
-      <x:c r="K6" s="60" t="n">
+      <x:c r="K6" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L6" s="60" t="n">
+      <x:c r="L6" s="31" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M6" s="60" t="n">
+      <x:c r="M6" s="31" t="n">
         <x:v>105.9792232908</x:v>
       </x:c>
-      <x:c r="N6" s="46" t="str">
+      <x:c r="N6" s="24" t="str">
         <x:v>coregonus autumnalis</x:v>
       </x:c>
-      <x:c r="O6" s="62" t="n">
+      <x:c r="O6" s="32" t="n">
         <x:v>3.67</x:v>
       </x:c>
-      <x:c r="P6" s="46" t="str">
+      <x:c r="P6" s="24" t="str">
         <x:v>exact_2020_supplement</x:v>
       </x:c>
-      <x:c r="Q6" s="62" t="str">
+      <x:c r="Q6" s="32" t="str">
         <x:v>2020 supplement MeanTL</x:v>
       </x:c>
-      <x:c r="R6" s="46" t="str">
+      <x:c r="R6" s="24" t="str">
         <x:v>high</x:v>
       </x:c>
-      <x:c r="S6" s="46" t="str">
+      <x:c r="S6" s="24" t="str">
         <x:v>Coregonus autumnalis</x:v>
       </x:c>
-      <x:c r="T6" s="62" t="n">
+      <x:c r="T6" s="32" t="n">
         <x:f>IF(O6="","",(1/'Metadata'!$B$5)^(O6-1))</x:f>
         <x:v>467.73514128719813</x:v>
       </x:c>
-      <x:c r="U6" s="60" t="n">
+      <x:c r="U6" s="31" t="n">
         <x:f>IF(T6="","",I6*T6)</x:f>
         <x:v>49570.20697942985</x:v>
       </x:c>
@@ -1148,7 +983,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41ca786a2e214375"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2fb1ece2344e4cfb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1158,195 +993,71 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="56" t="str">
+      <x:c r="A1" s="29" t="str">
         <x:v>commercial_group</x:v>
       </x:c>
-      <x:c r="B1" s="56" t="str">
-        <x:v>taxon_count_total</x:v>
-      </x:c>
-      <x:c r="C1" s="56" t="str">
-        <x:v>taxon_count_matched</x:v>
-      </x:c>
-      <x:c r="D1" s="56" t="str">
-        <x:v>catch_tonnes_total</x:v>
-      </x:c>
-      <x:c r="E1" s="56" t="str">
+      <x:c r="B1" s="29" t="str">
         <x:v>catch_tonnes_matched</x:v>
       </x:c>
-      <x:c r="F1" s="56" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="56" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="56" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="56" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="56" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="56" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="56" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="56" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="56" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="56" t="str">
-        <x:v>jensen_percent_difference</x:v>
+      <x:c r="C1" s="29" t="str">
+        <x:v>tl_weighted</x:v>
+      </x:c>
+      <x:c r="D1" s="29" t="str">
+        <x:v>sppr</x:v>
+      </x:c>
+      <x:c r="E1" s="29" t="str">
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
-      <x:c r="A2" s="46" t="str">
+      <x:c r="A2" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B2" s="64" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="64" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="60" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>1128.8195392729</x:v>
       </x:c>
-      <x:c r="E2" s="60" t="n">
-        <x:v>1128.8195392729</x:v>
-      </x:c>
-      <x:c r="F2" s="62" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="66" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="62" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.28</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
         <x:v>190.54607179632464</x:v>
       </x:c>
-      <x:c r="I2" s="60" t="n">
-        <x:f>SUMIF('Species'!$H$2:$H$6,A2,'Species'!$U$2:$U$6)</x:f>
+      <x:c r="E2" s="31" t="n">
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>215092.12897538813</x:v>
       </x:c>
-      <x:c r="J2" s="62" t="n">
-        <x:v>3.28</x:v>
-      </x:c>
-      <x:c r="K2" s="62" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>190.54607179632464</x:v>
-      </x:c>
-      <x:c r="L2" s="60" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>215092.12897538813</x:v>
-      </x:c>
-      <x:c r="M2" s="60" t="n">
-        <x:f>I2-L2</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="62" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="66" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
-      <x:c r="A3" s="46" t="str">
+      <x:c r="A3" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B3" s="64" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="64" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D3" s="60" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1487.3638769628003</x:v>
       </x:c>
-      <x:c r="E3" s="60" t="n">
-        <x:v>1487.3638769628003</x:v>
-      </x:c>
-      <x:c r="F3" s="62" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="66" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="62" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>196.32912701219442</x:v>
-      </x:c>
-      <x:c r="I3" s="60" t="n">
-        <x:f>SUMIF('Species'!$H$2:$H$6,A3,'Species'!$U$2:$U$6)</x:f>
-        <x:v>292012.85151357955</x:v>
-      </x:c>
-      <x:c r="J3" s="62" t="n">
+      <x:c r="C3" s="32" t="n">
         <x:v>3.27331885114682</x:v>
       </x:c>
-      <x:c r="K3" s="62" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
         <x:v>187.6371600549579</x:v>
       </x:c>
-      <x:c r="L3" s="60" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+      <x:c r="E3" s="31" t="n">
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>279084.7338416317</x:v>
       </x:c>
-      <x:c r="M3" s="60" t="n">
-        <x:f>I3-L3</x:f>
-        <x:v>12928.117671947868</x:v>
-      </x:c>
-      <x:c r="N3" s="62" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0463232706927066</x:v>
-      </x:c>
-      <x:c r="O3" s="66" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.046323270692706565</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G3">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O3">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98c2af3347bc4231"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95b3776a87d9462a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1356,249 +1067,90 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="56" t="str">
+      <x:c r="A1" s="29" t="str">
         <x:v>functional_group</x:v>
       </x:c>
-      <x:c r="B1" s="56" t="str">
-        <x:v>taxon_count_total</x:v>
-      </x:c>
-      <x:c r="C1" s="56" t="str">
-        <x:v>taxon_count_matched</x:v>
-      </x:c>
-      <x:c r="D1" s="56" t="str">
-        <x:v>catch_tonnes_total</x:v>
-      </x:c>
-      <x:c r="E1" s="56" t="str">
+      <x:c r="B1" s="29" t="str">
         <x:v>catch_tonnes_matched</x:v>
       </x:c>
-      <x:c r="F1" s="56" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="56" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="56" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="56" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="56" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="56" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="56" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="56" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="56" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="56" t="str">
-        <x:v>jensen_percent_difference</x:v>
+      <x:c r="C1" s="29" t="str">
+        <x:v>tl_weighted</x:v>
+      </x:c>
+      <x:c r="D1" s="29" t="str">
+        <x:v>sppr</x:v>
+      </x:c>
+      <x:c r="E1" s="29" t="str">
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
-      <x:c r="A2" s="46" t="str">
+      <x:c r="A2" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B2" s="64" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="64" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="60" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>508.346393164</x:v>
       </x:c>
-      <x:c r="E2" s="60" t="n">
-        <x:v>508.346393164</x:v>
-      </x:c>
-      <x:c r="F2" s="62" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="66" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="62" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.27</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
         <x:v>186.20871366628674</x:v>
       </x:c>
-      <x:c r="I2" s="60" t="n">
-        <x:f>SUMIF('Species'!$G$2:$G$6,A2,'Species'!$U$2:$U$6)</x:f>
+      <x:c r="E2" s="31" t="n">
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>94658.5279679649</x:v>
       </x:c>
-      <x:c r="J2" s="62" t="n">
-        <x:v>3.27</x:v>
-      </x:c>
-      <x:c r="K2" s="62" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>186.20871366628674</x:v>
-      </x:c>
-      <x:c r="L2" s="60" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>94658.5279679649</x:v>
-      </x:c>
-      <x:c r="M2" s="60" t="n">
-        <x:f>I2-L2</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="62" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="66" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
-      <x:c r="A3" s="46" t="str">
+      <x:c r="A3" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="64" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="64" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="60" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1128.8195392729</x:v>
       </x:c>
-      <x:c r="E3" s="60" t="n">
-        <x:v>1128.8195392729</x:v>
-      </x:c>
-      <x:c r="F3" s="62" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="66" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="62" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.28</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
         <x:v>190.54607179632464</x:v>
       </x:c>
-      <x:c r="I3" s="60" t="n">
-        <x:f>SUMIF('Species'!$G$2:$G$6,A3,'Species'!$U$2:$U$6)</x:f>
+      <x:c r="E3" s="31" t="n">
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>215092.12897538813</x:v>
       </x:c>
-      <x:c r="J3" s="62" t="n">
-        <x:v>3.28</x:v>
-      </x:c>
-      <x:c r="K3" s="62" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>190.54607179632464</x:v>
-      </x:c>
-      <x:c r="L3" s="60" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>215092.12897538813</x:v>
-      </x:c>
-      <x:c r="M3" s="60" t="n">
-        <x:f>I3-L3</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="62" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="66" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
-      <x:c r="A4" s="46" t="str">
+      <x:c r="A4" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="64" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="64" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="60" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>979.0174837988</x:v>
       </x:c>
-      <x:c r="E4" s="60" t="n">
-        <x:v>979.0174837988</x:v>
-      </x:c>
-      <x:c r="F4" s="62" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="66" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="62" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>201.5840644437085</x:v>
-      </x:c>
-      <x:c r="I4" s="60" t="n">
-        <x:f>SUMIF('Species'!$G$2:$G$6,A4,'Species'!$U$2:$U$6)</x:f>
-        <x:v>197354.32354561464</x:v>
-      </x:c>
-      <x:c r="J4" s="62" t="n">
+      <x:c r="C4" s="32" t="n">
         <x:v>3.2750421360093016</x:v>
       </x:c>
-      <x:c r="K4" s="62" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
         <x:v>188.38318532808898</x:v>
       </x:c>
-      <x:c r="L4" s="60" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+      <x:c r="E4" s="31" t="n">
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>184430.4320899087</x:v>
       </x:c>
-      <x:c r="M4" s="60" t="n">
-        <x:f>I4-L4</x:f>
-        <x:v>12923.891455705947</x:v>
-      </x:c>
-      <x:c r="N4" s="62" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0700746146352118</x:v>
-      </x:c>
-      <x:c r="O4" s="66" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.07007461463521178</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G4">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O4">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48680f3e00024bb6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R908a14c871d34146"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1631,67 +1183,67 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="56" t="str">
+      <x:c r="A1" s="29" t="str">
         <x:v>unit_id</x:v>
       </x:c>
-      <x:c r="B1" s="56" t="str">
+      <x:c r="B1" s="29" t="str">
         <x:v>region_name</x:v>
       </x:c>
-      <x:c r="C1" s="56" t="str">
+      <x:c r="C1" s="29" t="str">
         <x:v>region_type</x:v>
       </x:c>
-      <x:c r="D1" s="56" t="str">
+      <x:c r="D1" s="29" t="str">
         <x:v>year</x:v>
       </x:c>
-      <x:c r="E1" s="56" t="str">
+      <x:c r="E1" s="29" t="str">
         <x:v>taxon</x:v>
       </x:c>
-      <x:c r="F1" s="56" t="str">
+      <x:c r="F1" s="29" t="str">
         <x:v>common_name</x:v>
       </x:c>
-      <x:c r="G1" s="56" t="str">
+      <x:c r="G1" s="29" t="str">
         <x:v>functional_group</x:v>
       </x:c>
-      <x:c r="H1" s="56" t="str">
+      <x:c r="H1" s="29" t="str">
         <x:v>commercial_group</x:v>
       </x:c>
-      <x:c r="I1" s="56" t="str">
+      <x:c r="I1" s="29" t="str">
         <x:v>catch_tonnes</x:v>
       </x:c>
-      <x:c r="J1" s="56" t="str">
+      <x:c r="J1" s="29" t="str">
         <x:v>landings_tonnes</x:v>
       </x:c>
-      <x:c r="K1" s="56" t="str">
+      <x:c r="K1" s="29" t="str">
         <x:v>discards_tonnes</x:v>
       </x:c>
-      <x:c r="L1" s="56" t="str">
+      <x:c r="L1" s="29" t="str">
         <x:v>reported_tonnes</x:v>
       </x:c>
-      <x:c r="M1" s="56" t="str">
+      <x:c r="M1" s="29" t="str">
         <x:v>unreported_tonnes</x:v>
       </x:c>
-      <x:c r="N1" s="56" t="str">
+      <x:c r="N1" s="29" t="str">
         <x:v>taxon_key</x:v>
       </x:c>
-      <x:c r="O1" s="56" t="str">
+      <x:c r="O1" s="29" t="str">
         <x:v>tl</x:v>
       </x:c>
-      <x:c r="P1" s="56" t="str">
+      <x:c r="P1" s="29" t="str">
         <x:v>match_method</x:v>
       </x:c>
-      <x:c r="Q1" s="56" t="str">
+      <x:c r="Q1" s="29" t="str">
         <x:v>tl_source</x:v>
       </x:c>
-      <x:c r="R1" s="56" t="str">
+      <x:c r="R1" s="29" t="str">
         <x:v>match_confidence</x:v>
       </x:c>
-      <x:c r="S1" s="56" t="str">
+      <x:c r="S1" s="29" t="str">
         <x:v>reference_taxon</x:v>
       </x:c>
-      <x:c r="T1" s="56" t="str">
+      <x:c r="T1" s="29" t="str">
         <x:v>sppr</x:v>
       </x:c>
-      <x:c r="U1" s="56" t="str">
+      <x:c r="U1" s="29" t="str">
         <x:v>ppr</x:v>
       </x:c>
     </x:row>
@@ -1711,275 +1263,247 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="56" t="str">
+      <x:c r="A1" s="29" t="str">
         <x:v>unit_id</x:v>
       </x:c>
-      <x:c r="B1" s="56" t="str">
+      <x:c r="B1" s="29" t="str">
         <x:v>check</x:v>
       </x:c>
-      <x:c r="C1" s="56" t="str">
+      <x:c r="C1" s="29" t="str">
         <x:v>value</x:v>
       </x:c>
-      <x:c r="D1" s="56" t="str">
+      <x:c r="D1" s="29" t="str">
         <x:v>unit</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
-      <x:c r="A2" s="46" t="str">
-        <x:v>LME_057</x:v>
-      </x:c>
-      <x:c r="B2" s="46" t="str">
+      <x:c r="A2" s="24" t="str">
+        <x:v>LME_057</x:v>
+      </x:c>
+      <x:c r="B2" s="24" t="str">
         <x:v>raw_filtered_tonnes</x:v>
       </x:c>
-      <x:c r="C2" s="46" t="n">
+      <x:c r="C2" s="24" t="n">
         <x:v>2616.1834162357</x:v>
       </x:c>
-      <x:c r="D2" s="46" t="str">
+      <x:c r="D2" s="24" t="str">
         <x:v>tonnes</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
-      <x:c r="A3" s="46" t="str">
-        <x:v>LME_057</x:v>
-      </x:c>
-      <x:c r="B3" s="46" t="str">
+      <x:c r="A3" s="24" t="str">
+        <x:v>LME_057</x:v>
+      </x:c>
+      <x:c r="B3" s="24" t="str">
         <x:v>species_catch_tonnes</x:v>
       </x:c>
-      <x:c r="C3" s="46" t="n">
+      <x:c r="C3" s="24" t="n">
         <x:v>2616.1834162357</x:v>
       </x:c>
-      <x:c r="D3" s="46" t="str">
+      <x:c r="D3" s="24" t="str">
         <x:v>tonnes</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
-      <x:c r="A4" s="46" t="str">
-        <x:v>LME_057</x:v>
-      </x:c>
-      <x:c r="B4" s="46" t="str">
+      <x:c r="A4" s="24" t="str">
+        <x:v>LME_057</x:v>
+      </x:c>
+      <x:c r="B4" s="24" t="str">
         <x:v>catch_difference_tonnes</x:v>
       </x:c>
-      <x:c r="C4" s="46" t="n">
+      <x:c r="C4" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D4" s="46" t="str">
+      <x:c r="D4" s="24" t="str">
         <x:v>tonnes</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
-      <x:c r="A5" s="46" t="str">
-        <x:v>LME_057</x:v>
-      </x:c>
-      <x:c r="B5" s="46" t="str">
+      <x:c r="A5" s="24" t="str">
+        <x:v>LME_057</x:v>
+      </x:c>
+      <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="46" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="D5" s="46" t="str">
+      <x:c r="C5" s="33" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D5" s="24" t="str">
         <x:v>boolean</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
-      <x:c r="A6" s="46" t="str">
-        <x:v>LME_057</x:v>
-      </x:c>
-      <x:c r="B6" s="46" t="str">
+      <x:c r="A6" s="24" t="str">
+        <x:v>LME_057</x:v>
+      </x:c>
+      <x:c r="B6" s="24" t="str">
         <x:v>matched_catch_tonnes</x:v>
       </x:c>
-      <x:c r="C6" s="46" t="n">
+      <x:c r="C6" s="24" t="n">
         <x:v>2616.1834162357</x:v>
       </x:c>
-      <x:c r="D6" s="46" t="str">
+      <x:c r="D6" s="24" t="str">
         <x:v>tonnes</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
-      <x:c r="A7" s="46" t="str">
-        <x:v>LME_057</x:v>
-      </x:c>
-      <x:c r="B7" s="46" t="str">
+      <x:c r="A7" s="24" t="str">
+        <x:v>LME_057</x:v>
+      </x:c>
+      <x:c r="B7" s="24" t="str">
         <x:v>catch_coverage_fraction</x:v>
       </x:c>
-      <x:c r="C7" s="46" t="n">
+      <x:c r="C7" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D7" s="46" t="str">
+      <x:c r="D7" s="24" t="str">
         <x:v>fraction</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
-      <x:c r="A8" s="46" t="str">
-        <x:v>LME_057</x:v>
-      </x:c>
-      <x:c r="B8" s="46" t="str">
+      <x:c r="A8" s="24" t="str">
+        <x:v>LME_057</x:v>
+      </x:c>
+      <x:c r="B8" s="24" t="str">
         <x:v>taxa_count</x:v>
       </x:c>
-      <x:c r="C8" s="46" t="n">
+      <x:c r="C8" s="24" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D8" s="46" t="str">
+      <x:c r="D8" s="24" t="str">
         <x:v>count</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
-      <x:c r="A9" s="46" t="str">
-        <x:v>LME_057</x:v>
-      </x:c>
-      <x:c r="B9" s="46" t="str">
+      <x:c r="A9" s="24" t="str">
+        <x:v>LME_057</x:v>
+      </x:c>
+      <x:c r="B9" s="24" t="str">
         <x:v>matched_taxa_count</x:v>
       </x:c>
-      <x:c r="C9" s="46" t="n">
+      <x:c r="C9" s="24" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D9" s="46" t="str">
+      <x:c r="D9" s="24" t="str">
         <x:v>count</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
-      <x:c r="A10" s="46" t="str">
-        <x:v>LME_057</x:v>
-      </x:c>
-      <x:c r="B10" s="46" t="str">
+      <x:c r="A10" s="24" t="str">
+        <x:v>LME_057</x:v>
+      </x:c>
+      <x:c r="B10" s="24" t="str">
         <x:v>unmatched_taxa_count</x:v>
       </x:c>
-      <x:c r="C10" s="46" t="n">
+      <x:c r="C10" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D10" s="46" t="str">
+      <x:c r="D10" s="24" t="str">
         <x:v>count</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
-      <x:c r="A11" s="46" t="str">
-        <x:v>LME_057</x:v>
-      </x:c>
-      <x:c r="B11" s="46" t="str">
+      <x:c r="A11" s="24" t="str">
+        <x:v>LME_057</x:v>
+      </x:c>
+      <x:c r="B11" s="24" t="str">
         <x:v>species_ppr</x:v>
       </x:c>
-      <x:c r="C11" s="46" t="n">
+      <x:c r="C11" s="24" t="n">
         <x:v>507104.9804889677</x:v>
       </x:c>
-      <x:c r="D11" s="46" t="str">
+      <x:c r="D11" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
-      <x:c r="A12" s="46" t="str">
-        <x:v>LME_057</x:v>
-      </x:c>
-      <x:c r="B12" s="46" t="str">
+      <x:c r="A12" s="24" t="str">
+        <x:v>LME_057</x:v>
+      </x:c>
+      <x:c r="B12" s="24" t="str">
         <x:v>commercial_ppr</x:v>
       </x:c>
-      <x:c r="C12" s="46" t="n">
-        <x:v>507104.9804889677</x:v>
-      </x:c>
-      <x:c r="D12" s="46" t="str">
+      <x:c r="C12" s="24" t="n">
+        <x:v>494176.8628170198</x:v>
+      </x:c>
+      <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
-      <x:c r="A13" s="46" t="str">
-        <x:v>LME_057</x:v>
-      </x:c>
-      <x:c r="B13" s="46" t="str">
+      <x:c r="A13" s="24" t="str">
+        <x:v>LME_057</x:v>
+      </x:c>
+      <x:c r="B13" s="24" t="str">
         <x:v>functional_ppr</x:v>
       </x:c>
-      <x:c r="C13" s="46" t="n">
-        <x:v>507104.9804889676</x:v>
-      </x:c>
-      <x:c r="D13" s="46" t="str">
+      <x:c r="C13" s="24" t="n">
+        <x:v>494181.0890332617</x:v>
+      </x:c>
+      <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
-      <x:c r="A14" s="46" t="str">
-        <x:v>LME_057</x:v>
-      </x:c>
-      <x:c r="B14" s="46" t="str">
+      <x:c r="A14" s="24" t="str">
+        <x:v>LME_057</x:v>
+      </x:c>
+      <x:c r="B14" s="24" t="str">
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
-      <x:c r="C14" s="46" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D14" s="46" t="str">
+      <x:c r="C14" s="24" t="n">
+        <x:v>-12928.117671947868</x:v>
+      </x:c>
+      <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
-      <x:c r="A15" s="46" t="str">
-        <x:v>LME_057</x:v>
-      </x:c>
-      <x:c r="B15" s="46" t="str">
+      <x:c r="A15" s="24" t="str">
+        <x:v>LME_057</x:v>
+      </x:c>
+      <x:c r="B15" s="24" t="str">
         <x:v>functional_ppr_difference</x:v>
       </x:c>
-      <x:c r="C15" s="46" t="n">
-        <x:v>-5.820766091346741e-11</x:v>
-      </x:c>
-      <x:c r="D15" s="46" t="str">
+      <x:c r="C15" s="24" t="n">
+        <x:v>-12923.891455705976</x:v>
+      </x:c>
+      <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
-      <x:c r="A16" s="46" t="str">
-        <x:v>LME_057</x:v>
-      </x:c>
-      <x:c r="B16" s="46" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="46" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="D16" s="46" t="str">
+      <x:c r="A16" s="24" t="str">
+        <x:v>LME_057</x:v>
+      </x:c>
+      <x:c r="B16" s="24" t="str">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D16" s="24" t="str">
         <x:v>boolean</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
-      <x:c r="A17" s="46" t="str">
-        <x:v>LME_057</x:v>
-      </x:c>
-      <x:c r="B17" s="46" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="46" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="D17" s="46" t="str">
+      <x:c r="A17" s="24" t="str">
+        <x:v>LME_057</x:v>
+      </x:c>
+      <x:c r="B17" s="24" t="str">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="46" t="str">
-        <x:v>LME_057</x:v>
-      </x:c>
-      <x:c r="B18" s="46" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="46" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="46" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="46" t="str">
-        <x:v>LME_057</x:v>
-      </x:c>
-      <x:c r="B19" s="46" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="46" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="46" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3de247295fd748e3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49c79443159646e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1994,152 +1518,152 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str">
+      <x:c r="A1" s="3" t="str">
         <x:v>LME_057 - Laptev Sea</x:v>
       </x:c>
-      <x:c r="B1" s="4"/>
-      <x:c r="C1" s="4"/>
+      <x:c r="B1" s="3"/>
+      <x:c r="C1" s="3"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="12" t="str">
+      <x:c r="A3" s="7" t="str">
         <x:v>Field</x:v>
       </x:c>
-      <x:c r="B3" s="13" t="str">
+      <x:c r="B3" s="8" t="str">
         <x:v>Value</x:v>
       </x:c>
-      <x:c r="C3" s="14" t="str">
+      <x:c r="C3" s="9" t="str">
         <x:v>Notes / source</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="42" t="str">
+      <x:c r="A4" s="22" t="str">
         <x:v>Unit ID</x:v>
       </x:c>
-      <x:c r="B4" s="31" t="str">
-        <x:v>LME_057</x:v>
-      </x:c>
-      <x:c r="C4" s="32" t="str">
+      <x:c r="B4" s="17" t="str">
+        <x:v>LME_057</x:v>
+      </x:c>
+      <x:c r="C4" s="18" t="str">
         <x:v>Sea Around Us region identifier</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="42" t="str">
+      <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="68" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="C5" s="32" t="str">
+      <x:c r="C5" s="18" t="str">
         <x:v>Used by every SPPR formula</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="42" t="str">
+      <x:c r="A6" s="22" t="str">
         <x:v>Year</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="n">
+      <x:c r="B6" s="17" t="n">
         <x:v>2019</x:v>
       </x:c>
-      <x:c r="C6" s="32" t="str">
+      <x:c r="C6" s="18" t="str">
         <x:v>Latest year common to all 84 datasets</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="42" t="str">
+      <x:c r="A7" s="22" t="str">
         <x:v>Region type</x:v>
       </x:c>
-      <x:c r="B7" s="31" t="str">
+      <x:c r="B7" s="17" t="str">
         <x:v>LME</x:v>
       </x:c>
-      <x:c r="C7" s="32" t="str">
+      <x:c r="C7" s="18" t="str">
         <x:v>Sea Around Us spatial classification</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="42" t="str">
+      <x:c r="A8" s="22" t="str">
         <x:v>Catch scope</x:v>
       </x:c>
-      <x:c r="B8" s="31" t="str">
+      <x:c r="B8" s="17" t="str">
         <x:v>Landings + Discards</x:v>
       </x:c>
-      <x:c r="C8" s="32" t="str">
+      <x:c r="C8" s="18" t="str">
         <x:v>Reported + unreported; all sectors, gears, entities, and end uses</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="42" t="str">
+      <x:c r="A9" s="22" t="str">
         <x:v>SPPR formula</x:v>
       </x:c>
-      <x:c r="B9" s="31" t="str">
+      <x:c r="B9" s="17" t="str">
         <x:v>(1 / TE)^(TL - 1)</x:v>
       </x:c>
-      <x:c r="C9" s="32" t="str">
+      <x:c r="C9" s="18" t="str">
         <x:v>TE is the Metadata!B5 value</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="42" t="str">
+      <x:c r="A10" s="22" t="str">
         <x:v>PPR formula</x:v>
       </x:c>
-      <x:c r="B10" s="31" t="str">
+      <x:c r="B10" s="17" t="str">
         <x:v>Catch tonnes × SPPR</x:v>
       </x:c>
-      <x:c r="C10" s="32" t="str">
+      <x:c r="C10" s="18" t="str">
         <x:v>Unit: tonnes primary-production equivalent</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="42" t="str">
+      <x:c r="A11" s="22" t="str">
         <x:v>Wet-weight/carbon divisor</x:v>
       </x:c>
-      <x:c r="B11" s="31" t="str">
+      <x:c r="B11" s="17" t="str">
         <x:v>Not applied</x:v>
       </x:c>
-      <x:c r="C11" s="32" t="str">
+      <x:c r="C11" s="18" t="str">
         <x:v>The paper's /9 conversion is intentionally omitted</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="42" t="str">
+      <x:c r="A12" s="22" t="str">
         <x:v>Primary TL source</x:v>
       </x:c>
-      <x:c r="B12" s="31" t="str">
+      <x:c r="B12" s="17" t="str">
         <x:v>2020 supplement MeanTL</x:v>
       </x:c>
-      <x:c r="C12" s="32" t="str">
+      <x:c r="C12" s="18" t="str">
         <x:v>No SPPR regression from the supplement is used</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="42" t="str">
+      <x:c r="A13" s="22" t="str">
         <x:v>Secondary TL source</x:v>
       </x:c>
-      <x:c r="B13" s="31" t="str">
+      <x:c r="B13" s="17" t="str">
         <x:v>Sea Around Us exploited organisms</x:v>
       </x:c>
-      <x:c r="C13" s="32" t="str">
+      <x:c r="C13" s="18" t="str">
         <x:v>Exact taxon matches, followed by documented fallbacks</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="42" t="str">
+      <x:c r="A14" s="22" t="str">
         <x:v>Catch data URL</x:v>
       </x:c>
-      <x:c r="B14" s="31" t="str">
+      <x:c r="B14" s="17" t="str">
         <x:v>https://www.seaaroundus.org/data/</x:v>
       </x:c>
-      <x:c r="C14" s="32" t="str">
+      <x:c r="C14" s="18" t="str">
         <x:v>Frozen archive: raw_data/SAU_downloads/LME_057-catch.zip</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="43" t="str">
+      <x:c r="A15" s="23" t="str">
         <x:v>Method source</x:v>
       </x:c>
-      <x:c r="B15" s="34" t="str">
+      <x:c r="B15" s="20" t="str">
         <x:v>Pauly &amp; Christensen (1995)</x:v>
       </x:c>
-      <x:c r="C15" s="35" t="str">
+      <x:c r="C15" s="21" t="str">
         <x:v>Nature 374:255-257</x:v>
       </x:c>
     </x:row>
